--- a/rpa_basic/1_excel/sample.xlsx
+++ b/rpa_basic/1_excel/sample.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="NadoSheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,137 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>영어</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>수학</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C2" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>83</v>
-      </c>
-      <c r="C3" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>39</v>
-      </c>
-      <c r="C4" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>44</v>
-      </c>
-      <c r="C5" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>33</v>
-      </c>
-      <c r="C6" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>39</v>
-      </c>
-      <c r="C7" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="n">
-        <v>69</v>
-      </c>
-      <c r="C8" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>47</v>
-      </c>
-      <c r="C9" t="n">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="n">
-        <v>31</v>
-      </c>
-      <c r="C10" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="n">
-        <v>90</v>
-      </c>
-      <c r="C11" t="n">
-        <v>45</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>